--- a/events/Augsburg_2023_WWC/Augsburg_2023_WWC_start.xlsx
+++ b/events/Augsburg_2023_WWC/Augsburg_2023_WWC_start.xlsx
@@ -835,6 +835,11 @@
           <t>FORMENTON Giulia</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>43572</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -893,6 +898,11 @@
           <t>VANKOVA Klara</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>89349</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -951,6 +961,11 @@
           <t>NEMCOVA Marie</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>78808</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1009,6 +1024,11 @@
           <t>MUELLER Hannah</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>63133</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1067,6 +1087,11 @@
           <t>VINET Lise</t>
         </is>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>53291</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1125,6 +1150,11 @@
           <t>VALDENAIRE Mathilde</t>
         </is>
       </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>94782</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1183,6 +1213,11 @@
           <t>STEBLAJ Ana</t>
         </is>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>94495</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1241,6 +1276,11 @@
           <t>KROENER Valentina</t>
         </is>
       </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>41612</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1299,6 +1339,11 @@
           <t>NOVOSADOVA Kristina</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>98301</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1357,6 +1402,11 @@
           <t>FUSSER Sabine</t>
         </is>
       </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>36676</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1415,6 +1465,11 @@
           <t>DZIADKOVA Zuzana</t>
         </is>
       </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>98317</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1473,6 +1528,11 @@
           <t>MILNE Laura</t>
         </is>
       </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>75768</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1531,6 +1591,11 @@
           <t>OZIMC Nika</t>
         </is>
       </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>112182</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1589,6 +1654,11 @@
           <t>MASSINI Christina</t>
         </is>
       </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>87895</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1647,6 +1717,11 @@
           <t>JANCAR Ziva</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>83919</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1705,6 +1780,11 @@
           <t>HULPIAU Clemence</t>
         </is>
       </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>83552</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1763,6 +1843,11 @@
           <t>KOPUNOVA Katarina</t>
         </is>
       </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>35471</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1821,6 +1906,11 @@
           <t>MURRAY Victoria</t>
         </is>
       </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>75660</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1879,6 +1969,11 @@
           <t>CHRISTIE Kerry</t>
         </is>
       </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>99724</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1937,6 +2032,11 @@
           <t>SINNESAEL Laurane</t>
         </is>
       </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>63339</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2053,6 +2153,11 @@
           <t>ECKERT Jil-Sophie</t>
         </is>
       </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>39763</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2111,6 +2216,11 @@
           <t>CREEK Amanda</t>
         </is>
       </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>77289</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2169,6 +2279,11 @@
           <t>DIAZ QUINTIAN Noa</t>
         </is>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>112772</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2227,6 +2342,11 @@
           <t>ETTLIN Glenys</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>112430</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2285,6 +2405,11 @@
           <t>CLAVADETSCHER Mona</t>
         </is>
       </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>112429</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2343,6 +2468,11 @@
           <t>DEVESA FERNANDEZ Emma</t>
         </is>
       </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>123935</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2401,6 +2531,11 @@
           <t>POCKLINGTON Katie Rose</t>
         </is>
       </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>112780</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2459,6 +2594,11 @@
           <t>ROMERO GOMEZ Nuria</t>
         </is>
       </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>131273</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2517,6 +2657,11 @@
           <t>LEBOUC Lisa</t>
         </is>
       </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>56150</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2575,6 +2720,11 @@
           <t>ROLLINS Harriet</t>
         </is>
       </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>64680</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2633,6 +2783,11 @@
           <t>SIMON Birgit</t>
         </is>
       </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>131545</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2691,6 +2846,11 @@
           <t>ROLENC Ondrej</t>
         </is>
       </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>35512</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2749,6 +2909,11 @@
           <t>SAUTEUR Nicolas</t>
         </is>
       </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>63173</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2807,6 +2972,11 @@
           <t>VANEK Matej</t>
         </is>
       </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>98305</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2865,6 +3035,11 @@
           <t>DANIK Ladislav</t>
         </is>
       </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>82996</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2923,6 +3098,11 @@
           <t>MAPELLI Tommaso</t>
         </is>
       </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>75795</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2981,6 +3161,11 @@
           <t>FERRION Charles</t>
         </is>
       </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>94783</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3039,6 +3224,11 @@
           <t>HEILINGER Tim</t>
         </is>
       </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>37668</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3097,6 +3287,11 @@
           <t>MULLER Jonah</t>
         </is>
       </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>76129</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3155,6 +3350,11 @@
           <t>BIANCHETTI Giacomo</t>
         </is>
       </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>75796</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3213,6 +3413,11 @@
           <t>SALAJ Frantisek</t>
         </is>
       </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>96105</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3271,6 +3476,11 @@
           <t>ZANNI Matteo</t>
         </is>
       </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>98759</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3329,6 +3539,11 @@
           <t>BEIER Matous</t>
         </is>
       </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>98299</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3387,6 +3602,11 @@
           <t>ZDRAVKOVIC Pavle</t>
         </is>
       </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>39964</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3445,6 +3665,11 @@
           <t>SCHWARZ Ole</t>
         </is>
       </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>76065</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3503,6 +3728,11 @@
           <t>SCAPINI Cesare Lorenzo</t>
         </is>
       </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>110468</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3561,6 +3791,11 @@
           <t>PRESECKI Janko</t>
         </is>
       </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>112241</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3619,6 +3854,11 @@
           <t>COF Blaz</t>
         </is>
       </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>36897</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3677,6 +3917,11 @@
           <t>MCEWAN Devin</t>
         </is>
       </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>35068</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3735,6 +3980,11 @@
           <t>ALVAREZ VAZQUEZ Efren</t>
         </is>
       </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>123928</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3793,6 +4043,11 @@
           <t>JANISZEWSKI Robert</t>
         </is>
       </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>61749</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3851,6 +4106,11 @@
           <t>JIMENEZ Iker</t>
         </is>
       </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>79679</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3909,6 +4169,11 @@
           <t>PADILLA Alan</t>
         </is>
       </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>71117</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3967,6 +4232,11 @@
           <t>CROWHURST Andrew</t>
         </is>
       </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>121055</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4025,6 +4295,11 @@
           <t>SUELZER Janosch</t>
         </is>
       </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>43111</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4083,6 +4358,11 @@
           <t>RAMOS COLLADO Rodrigo</t>
         </is>
       </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>37657</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4141,6 +4421,11 @@
           <t>WEBER Normen</t>
         </is>
       </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>36679</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4199,6 +4484,11 @@
           <t>ZNIDARCIC Nejc</t>
         </is>
       </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>37764</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4257,6 +4547,11 @@
           <t>SATKE Adam</t>
         </is>
       </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>70681</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4315,6 +4610,11 @@
           <t>URANKAR Anze</t>
         </is>
       </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>44341</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4373,6 +4673,11 @@
           <t>MATEJICEK Vojtech</t>
         </is>
       </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>87966</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4431,6 +4736,11 @@
           <t>MONTULET Leo</t>
         </is>
       </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>70119</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4489,6 +4799,11 @@
           <t>OVEN Simon</t>
         </is>
       </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>38164</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4547,6 +4862,11 @@
           <t>BEERSCHWENGER Bjoern</t>
         </is>
       </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>37662</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4605,6 +4925,11 @@
           <t>LEMMEN Yannic</t>
         </is>
       </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>45115</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4663,6 +4988,11 @@
           <t>BARONE Luca</t>
         </is>
       </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>94780</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4721,6 +5051,11 @@
           <t>BOLZERN Linus</t>
         </is>
       </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>56069</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4779,6 +5114,11 @@
           <t>CIOTOLI Francesco</t>
         </is>
       </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>70132</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4837,6 +5177,11 @@
           <t>ABBIATI Giacomo</t>
         </is>
       </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>94769</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4895,6 +5240,11 @@
           <t>FIDALGO DE LEON Guillermo</t>
         </is>
       </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>37655</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4953,6 +5303,11 @@
           <t>BRETSCHER Cornel</t>
         </is>
       </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>76131</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5011,6 +5366,11 @@
           <t>KUPSCH Tjas Til</t>
         </is>
       </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>106195</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5069,6 +5429,11 @@
           <t>MARJANOVIC Marko</t>
         </is>
       </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5127,6 +5492,11 @@
           <t>KROENER Tobias</t>
         </is>
       </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>118624</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5185,6 +5555,11 @@
           <t>BLUM Marcel</t>
         </is>
       </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>77335</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5243,6 +5618,11 @@
           <t>VEJNAR Samuel</t>
         </is>
       </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>112192</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5301,6 +5681,11 @@
           <t>CARTELLIERI Benjamin</t>
         </is>
       </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>105491</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5359,6 +5744,11 @@
           <t>ZLATAROV Aleksandar</t>
         </is>
       </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>43799</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5417,6 +5807,11 @@
           <t>GONZALEZ DIAZ Marcos</t>
         </is>
       </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>37664</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5475,6 +5870,11 @@
           <t>HOLMES Jacob</t>
         </is>
       </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>53139</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5533,6 +5933,11 @@
           <t>SPASIKJ Ljubomir</t>
         </is>
       </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>35591</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5591,6 +5996,11 @@
           <t>AMSTAD Janis</t>
         </is>
       </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>97548</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5649,6 +6059,11 @@
           <t>TAHIROVIC Alen</t>
         </is>
       </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>87291</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5707,6 +6122,11 @@
           <t>PORUBSKY Allan</t>
         </is>
       </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>86453</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5765,6 +6185,11 @@
           <t>MIGLIOSI Alberto</t>
         </is>
       </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>94768</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5823,6 +6248,11 @@
           <t>LAZAROV Kristijan</t>
         </is>
       </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>118951</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5881,6 +6311,11 @@
           <t>BARTOS Simon</t>
         </is>
       </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>113254</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5939,6 +6374,11 @@
           <t>RODRIGUEZ LEON Jesus</t>
         </is>
       </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>37654</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5997,6 +6437,11 @@
           <t>KASATSKYI Denys</t>
         </is>
       </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>119452</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6055,6 +6500,11 @@
           <t>BIGGIN Graeme</t>
         </is>
       </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>118918</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6113,6 +6563,11 @@
           <t>GUGINOV Blagoj</t>
         </is>
       </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>130269</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6229,6 +6684,11 @@
           <t>CORTI Lorenzo</t>
         </is>
       </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>112761</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6287,6 +6747,11 @@
           <t>NOVAK Matyas</t>
         </is>
       </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>105998</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6345,6 +6810,11 @@
           <t>CLAVADETSCHER Luis</t>
         </is>
       </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>97549</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6403,6 +6873,11 @@
           <t>KLEUT Neven</t>
         </is>
       </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>112758</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6461,6 +6936,11 @@
           <t>RODRIGUEZ LOPEZ Gabriel</t>
         </is>
       </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>123929</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6519,6 +6999,11 @@
           <t>BLAIS Elias</t>
         </is>
       </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>98755</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6577,6 +7062,11 @@
           <t>MARIEN Martin</t>
         </is>
       </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>130604</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6635,6 +7125,11 @@
           <t>PIASKOWSKI Joshua</t>
         </is>
       </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>130603</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6693,6 +7188,11 @@
           <t>SHEPPY Alexander</t>
         </is>
       </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>77242</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6751,6 +7251,11 @@
           <t>LAMERS Ivo</t>
         </is>
       </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>70112</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6809,6 +7314,11 @@
           <t>PAAUW Pieter</t>
         </is>
       </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>130311</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6867,6 +7377,11 @@
           <t>PANATO Cecilia</t>
         </is>
       </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>75522</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6925,6 +7440,11 @@
           <t>NEMCOVA Marie</t>
         </is>
       </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>78808</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6983,6 +7503,11 @@
           <t>FONTAINE Laura</t>
         </is>
       </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>98758</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7041,6 +7566,11 @@
           <t>GAUBERT Elsa</t>
         </is>
       </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>76817</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7099,6 +7629,11 @@
           <t>DZIADKOVA Zuzana</t>
         </is>
       </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>98317</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7157,6 +7692,11 @@
           <t>KOPUNOVA Katarina</t>
         </is>
       </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>35471</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7215,6 +7755,11 @@
           <t>BEZIAT Margot</t>
         </is>
       </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>86154</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7273,6 +7818,11 @@
           <t>SCHOLCZOVA Viktoria</t>
         </is>
       </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>89134</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7331,6 +7881,11 @@
           <t>RETKOVA Anna</t>
         </is>
       </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>105733</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7389,6 +7944,11 @@
           <t>BARM Sabrina</t>
         </is>
       </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>35175</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7447,6 +8007,11 @@
           <t>DIAZ QUINTIAN Noa</t>
         </is>
       </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>112772</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7505,6 +8070,11 @@
           <t>GAWEHN Franziska</t>
         </is>
       </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>130600</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7563,6 +8133,11 @@
           <t>PANATO Alice</t>
         </is>
       </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>56059</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7621,6 +8196,11 @@
           <t>PLACHTOVA Alexandra</t>
         </is>
       </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>75570</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7679,6 +8259,11 @@
           <t>NEMCOVA Marie</t>
         </is>
       </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>78808</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7737,6 +8322,11 @@
           <t>MUELLER Hannah</t>
         </is>
       </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>63133</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7795,6 +8385,11 @@
           <t>STEBLAJ Ana</t>
         </is>
       </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>94495</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7853,6 +8448,11 @@
           <t>KROENER Valentina</t>
         </is>
       </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>41612</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7911,6 +8511,11 @@
           <t>NOVOSADOVA Kristina</t>
         </is>
       </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>98301</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7969,6 +8574,11 @@
           <t>FUSSER Sabine</t>
         </is>
       </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>36676</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8027,6 +8637,11 @@
           <t>DZIADKOVA Zuzana</t>
         </is>
       </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>98317</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8085,6 +8700,11 @@
           <t>MILNE Laura</t>
         </is>
       </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>75768</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8143,6 +8763,11 @@
           <t>OZIMC Nika</t>
         </is>
       </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>112182</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8201,6 +8826,11 @@
           <t>MASSINI Christina</t>
         </is>
       </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>87895</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8259,6 +8889,11 @@
           <t>JANCAR Ziva</t>
         </is>
       </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>83919</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8317,6 +8952,11 @@
           <t>HULPIAU Clemence</t>
         </is>
       </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>83552</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8375,6 +9015,11 @@
           <t>KOPUNOVA Katarina</t>
         </is>
       </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>35471</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8433,6 +9078,11 @@
           <t>MURRAY Victoria</t>
         </is>
       </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>75660</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8491,6 +9141,11 @@
           <t>CHRISTIE Kerry</t>
         </is>
       </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>99724</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8549,6 +9204,11 @@
           <t>SINNESAEL Laurane</t>
         </is>
       </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>63339</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8665,6 +9325,11 @@
           <t>CREEK Amanda</t>
         </is>
       </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>77289</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8723,6 +9388,11 @@
           <t>DIAZ QUINTIAN Noa</t>
         </is>
       </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>112772</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8781,6 +9451,11 @@
           <t>ETTLIN Glenys</t>
         </is>
       </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>112430</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8839,6 +9514,11 @@
           <t>CLAVADETSCHER Mona</t>
         </is>
       </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>112429</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8897,6 +9577,11 @@
           <t>DEVESA FERNANDEZ Emma</t>
         </is>
       </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>123935</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8955,6 +9640,11 @@
           <t>POCKLINGTON Katie Rose</t>
         </is>
       </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>112780</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9013,6 +9703,11 @@
           <t>ROMERO GOMEZ Nuria</t>
         </is>
       </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>131273</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9071,6 +9766,11 @@
           <t>LEBOUC Lisa</t>
         </is>
       </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>56150</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9129,6 +9829,11 @@
           <t>ROLLINS Harriet</t>
         </is>
       </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>64680</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9187,6 +9892,11 @@
           <t>SIMON Birgit</t>
         </is>
       </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>131545</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9245,6 +9955,11 @@
           <t>ROLENC Ondrej</t>
         </is>
       </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>35512</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9303,6 +10018,11 @@
           <t>DANIK Ladislav</t>
         </is>
       </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>82996</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9361,6 +10081,11 @@
           <t>MAPELLI Tommaso</t>
         </is>
       </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>75795</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9419,6 +10144,11 @@
           <t>FERRION Charles</t>
         </is>
       </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>94783</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9477,6 +10207,11 @@
           <t>HEILINGER Tim</t>
         </is>
       </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>37668</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9535,6 +10270,11 @@
           <t>MULLER Jonah</t>
         </is>
       </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>76129</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9593,6 +10333,11 @@
           <t>BIANCHETTI Giacomo</t>
         </is>
       </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>75796</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9651,6 +10396,11 @@
           <t>SALAJ Frantisek</t>
         </is>
       </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>96105</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9709,6 +10459,11 @@
           <t>BEIER Matous</t>
         </is>
       </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>98299</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9767,6 +10522,11 @@
           <t>SCHWARZ Ole</t>
         </is>
       </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>76065</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9825,6 +10585,11 @@
           <t>SCAPINI Cesare Lorenzo</t>
         </is>
       </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>110468</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9883,6 +10648,11 @@
           <t>MCEWAN Devin</t>
         </is>
       </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>35068</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9941,6 +10711,11 @@
           <t>JANISZEWSKI Robert</t>
         </is>
       </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>61749</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9999,6 +10774,11 @@
           <t>JIMENEZ Iker</t>
         </is>
       </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>79679</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10057,6 +10837,11 @@
           <t>PADILLA Alan</t>
         </is>
       </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>71117</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10115,6 +10900,11 @@
           <t>CROWHURST Andrew</t>
         </is>
       </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>121055</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10173,6 +10963,11 @@
           <t>SUELZER Janosch</t>
         </is>
       </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>43111</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10231,6 +11026,11 @@
           <t>RAMOS COLLADO Rodrigo</t>
         </is>
       </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>37657</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10289,6 +11089,11 @@
           <t>SATKE Adam</t>
         </is>
       </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>70681</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10347,6 +11152,11 @@
           <t>URANKAR Anze</t>
         </is>
       </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>44341</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10405,6 +11215,11 @@
           <t>MATEJICEK Vojtech</t>
         </is>
       </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>87966</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10463,6 +11278,11 @@
           <t>MONTULET Leo</t>
         </is>
       </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>70119</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10521,6 +11341,11 @@
           <t>OVEN Simon</t>
         </is>
       </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>38164</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10579,6 +11404,11 @@
           <t>BEERSCHWENGER Bjoern</t>
         </is>
       </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>37662</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10637,6 +11467,11 @@
           <t>BARONE Luca</t>
         </is>
       </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>94780</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10695,6 +11530,11 @@
           <t>FIDALGO DE LEON Guillermo</t>
         </is>
       </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>37655</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10753,6 +11593,11 @@
           <t>BRETSCHER Cornel</t>
         </is>
       </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>76131</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10811,6 +11656,11 @@
           <t>KUPSCH Tjas Til</t>
         </is>
       </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>106195</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10869,6 +11719,11 @@
           <t>MARJANOVIC Marko</t>
         </is>
       </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10927,6 +11782,11 @@
           <t>KROENER Tobias</t>
         </is>
       </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>118624</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -10985,6 +11845,11 @@
           <t>BLUM Marcel</t>
         </is>
       </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>77335</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11043,6 +11908,11 @@
           <t>VEJNAR Samuel</t>
         </is>
       </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>112192</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11101,6 +11971,11 @@
           <t>CARTELLIERI Benjamin</t>
         </is>
       </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>105491</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11159,6 +12034,11 @@
           <t>ZLATAROV Aleksandar</t>
         </is>
       </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>43799</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11217,6 +12097,11 @@
           <t>GONZALEZ DIAZ Marcos</t>
         </is>
       </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>37664</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11275,6 +12160,11 @@
           <t>HOLMES Jacob</t>
         </is>
       </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>53139</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11333,6 +12223,11 @@
           <t>SPASIKJ Ljubomir</t>
         </is>
       </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>35591</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11391,6 +12286,11 @@
           <t>AMSTAD Janis</t>
         </is>
       </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>97548</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11449,6 +12349,11 @@
           <t>PORUBSKY Allan</t>
         </is>
       </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>86453</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11507,6 +12412,11 @@
           <t>MIGLIOSI Alberto</t>
         </is>
       </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>94768</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11565,6 +12475,11 @@
           <t>LAZAROV Kristijan</t>
         </is>
       </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>118951</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11623,6 +12538,11 @@
           <t>BARTOS Simon</t>
         </is>
       </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>113254</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11681,6 +12601,11 @@
           <t>RODRIGUEZ LEON Jesus</t>
         </is>
       </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>37654</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11739,6 +12664,11 @@
           <t>KASATSKYI Denys</t>
         </is>
       </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>119452</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11797,6 +12727,11 @@
           <t>BIGGIN Graeme</t>
         </is>
       </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>118918</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11855,6 +12790,11 @@
           <t>GUGINOV Blagoj</t>
         </is>
       </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>130269</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -11971,6 +12911,11 @@
           <t>CORTI Lorenzo</t>
         </is>
       </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>112761</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12029,6 +12974,11 @@
           <t>NOVAK Matyas</t>
         </is>
       </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>105998</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12087,6 +13037,11 @@
           <t>CLAVADETSCHER Luis</t>
         </is>
       </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>97549</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -12145,6 +13100,11 @@
           <t>KLEUT Neven</t>
         </is>
       </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>112758</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12203,6 +13163,11 @@
           <t>RODRIGUEZ LOPEZ Gabriel</t>
         </is>
       </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>123929</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12261,6 +13226,11 @@
           <t>BLAIS Elias</t>
         </is>
       </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>98755</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12319,6 +13289,11 @@
           <t>MARIEN Martin</t>
         </is>
       </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>130604</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12377,6 +13352,11 @@
           <t>PIASKOWSKI Joshua</t>
         </is>
       </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>130603</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12435,6 +13415,11 @@
           <t>SHEPPY Alexander</t>
         </is>
       </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>77242</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12493,6 +13478,11 @@
           <t>LAMERS Ivo</t>
         </is>
       </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>70112</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12551,6 +13541,11 @@
           <t>PAAUW Pieter</t>
         </is>
       </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>130311</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12609,6 +13604,11 @@
           <t>WAGNER Trevor</t>
         </is>
       </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>104530</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12667,6 +13667,11 @@
           <t>GAUBERT Elsa</t>
         </is>
       </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>76817</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12725,6 +13730,11 @@
           <t>KOPUNOVA Katarina</t>
         </is>
       </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>35471</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12783,6 +13793,11 @@
           <t>BEZIAT Margot</t>
         </is>
       </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>86154</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12841,6 +13856,11 @@
           <t>SCHOLCZOVA Viktoria</t>
         </is>
       </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>89134</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12899,6 +13919,11 @@
           <t>BARM Sabrina</t>
         </is>
       </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>35175</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -12957,6 +13982,11 @@
           <t>DIAZ QUINTIAN Noa</t>
         </is>
       </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>112772</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -13015,6 +14045,11 @@
           <t>GAWEHN Franziska</t>
         </is>
       </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>130600</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13073,6 +14108,11 @@
           <t>PANATO Alice</t>
         </is>
       </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>56059</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -13131,6 +14171,11 @@
           <t>PLACHTOVA Alexandra</t>
         </is>
       </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>75570</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13189,6 +14234,11 @@
           <t>ROLLINS Harriet</t>
         </is>
       </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>64680</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13252,6 +14302,16 @@
           <t>ROLENC Ondrej</t>
         </is>
       </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>42246</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>35512</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13315,6 +14375,16 @@
           <t>TROUBADY Pierre</t>
         </is>
       </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>56142</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>39643</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13378,6 +14448,16 @@
           <t>SMAKAL Petr</t>
         </is>
       </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>96105</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>96106</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13441,6 +14521,16 @@
           <t>ROUSSIN Tanguy</t>
         </is>
       </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>89475</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>89476</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13504,6 +14594,16 @@
           <t>BIANCHETTI Giacomo</t>
         </is>
       </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>75795</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>75796</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13567,6 +14667,16 @@
           <t>MULLER Jonah</t>
         </is>
       </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>76131</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>76129</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13630,6 +14740,16 @@
           <t>SCHWARZ Ole</t>
         </is>
       </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>112668</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>76065</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13693,6 +14813,16 @@
           <t>CARDOSELLI Tomas</t>
         </is>
       </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>112202</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>131360</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13756,6 +14886,16 @@
           <t>RASNER Karel</t>
         </is>
       </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>98305</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>98298</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13819,6 +14959,16 @@
           <t>ALVAREZ VAZQUEZ Efren</t>
         </is>
       </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>123929</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>123928</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13882,6 +15032,16 @@
           <t>JIMENEZ Iker</t>
         </is>
       </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>71117</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>79679</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13945,6 +15105,16 @@
           <t>VIENS Theo</t>
         </is>
       </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>63173</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>56129</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -14008,6 +15178,16 @@
           <t>VICENTE VELASCO Ruben</t>
         </is>
       </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>37657</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>131274</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -14071,6 +15251,16 @@
           <t>WEBER Normen</t>
         </is>
       </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>37668</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>36679</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14134,6 +15324,16 @@
           <t>RODRIGUEZ VEGA Saul</t>
         </is>
       </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>37654</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>112774</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14197,6 +15397,16 @@
           <t>BEZIAT Margot</t>
         </is>
       </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>76817</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>86154</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -14260,6 +15470,16 @@
           <t>CLAVADETSCHER Mona</t>
         </is>
       </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>63133</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>112429</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -14323,6 +15543,16 @@
           <t>RETKOVA Anna</t>
         </is>
       </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>75570</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>105733</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -14386,6 +15616,16 @@
           <t>STRILKOVA Jana</t>
         </is>
       </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>123430</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>104447</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -14449,6 +15689,16 @@
           <t>CHRISTIE Emma</t>
         </is>
       </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>99724</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>99726</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -14512,6 +15762,16 @@
           <t>ROMERO GOMEZ Nuria</t>
         </is>
       </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>123935</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>131273</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -14575,6 +15835,16 @@
           <t>FEINE Constanze</t>
         </is>
       </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>35175</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>93970</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -14638,6 +15908,16 @@
           <t>KROENER Valentina</t>
         </is>
       </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>41613</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>41612</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -14701,6 +15981,16 @@
           <t>DILAI Magdalen</t>
         </is>
       </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>75768</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>75657</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -14764,6 +16054,16 @@
           <t>PANATO Cecilia</t>
         </is>
       </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>56059</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>75522</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -14827,6 +16127,16 @@
           <t>ROLENC Ondrej</t>
         </is>
       </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>42246</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>35512</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -14890,6 +16200,16 @@
           <t>SMAKAL Petr</t>
         </is>
       </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>96105</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>96106</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -14953,6 +16273,16 @@
           <t>BIANCHETTI Giacomo</t>
         </is>
       </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>75795</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>75796</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -15016,6 +16346,16 @@
           <t>MULLER Jonah</t>
         </is>
       </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>76131</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>76129</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -15079,6 +16419,16 @@
           <t>CARDOSELLI Tomas</t>
         </is>
       </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>112202</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>131360</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -15142,6 +16492,16 @@
           <t>ALVAREZ VAZQUEZ Efren</t>
         </is>
       </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>123929</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>123928</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -15205,6 +16565,16 @@
           <t>JIMENEZ Iker</t>
         </is>
       </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>71117</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>79679</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -15268,6 +16638,16 @@
           <t>SUELZER Janosch</t>
         </is>
       </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>53557</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>43111</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -15331,6 +16711,16 @@
           <t>VICENTE VELASCO Ruben</t>
         </is>
       </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>37657</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>131274</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -15394,6 +16784,16 @@
           <t>WEBER Normen</t>
         </is>
       </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>37668</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>36679</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -15457,6 +16857,16 @@
           <t>RODRIGUEZ VEGA Saul</t>
         </is>
       </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>37654</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>112774</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -15521,6 +16931,11 @@
           <t>FORMENTON Giulia</t>
         </is>
       </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>43572</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -15585,6 +17000,11 @@
           <t>VANKOVA Klara</t>
         </is>
       </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>89349</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -15649,6 +17069,11 @@
           <t>NEMCOVA Marie</t>
         </is>
       </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>78808</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -15713,6 +17138,11 @@
           <t>MUELLER Hannah</t>
         </is>
       </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>63133</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -15777,6 +17207,11 @@
           <t>VINET Lise</t>
         </is>
       </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>53291</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -15841,6 +17276,11 @@
           <t>VALDENAIRE Mathilde</t>
         </is>
       </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>94782</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -15905,6 +17345,11 @@
           <t>STEBLAJ Ana</t>
         </is>
       </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>94495</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -15969,6 +17414,11 @@
           <t>NOVOSADOVA Kristina</t>
         </is>
       </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>98301</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -16033,6 +17483,11 @@
           <t>FUSSER Sabine</t>
         </is>
       </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>36676</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -16097,6 +17552,11 @@
           <t>MASSINI Christina</t>
         </is>
       </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>87895</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -16161,6 +17621,11 @@
           <t>HULPIAU Clemence</t>
         </is>
       </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>83552</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -16225,6 +17690,11 @@
           <t>SINNESAEL Laurane</t>
         </is>
       </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>63339</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -16289,6 +17759,11 @@
           <t>ECKERT Jil-Sophie</t>
         </is>
       </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>39763</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -16353,6 +17828,11 @@
           <t>CLAVADETSCHER Mona</t>
         </is>
       </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>112429</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -16417,6 +17897,11 @@
           <t>SIMON Birgit</t>
         </is>
       </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>131545</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -16481,6 +17966,11 @@
           <t>ROLENC Ondrej</t>
         </is>
       </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>35512</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -16545,6 +18035,11 @@
           <t>SAUTEUR Nicolas</t>
         </is>
       </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>63173</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -16609,6 +18104,11 @@
           <t>VANEK Matej</t>
         </is>
       </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>98305</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -16673,6 +18173,11 @@
           <t>MAPELLI Tommaso</t>
         </is>
       </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>75795</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -16737,6 +18242,11 @@
           <t>FERRION Charles</t>
         </is>
       </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>94783</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -16795,6 +18305,11 @@
           <t>HEILINGER Tim</t>
         </is>
       </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>37668</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -16859,6 +18374,11 @@
           <t>BIANCHETTI Giacomo</t>
         </is>
       </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>75796</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -16923,6 +18443,11 @@
           <t>SALAJ Frantisek</t>
         </is>
       </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>96105</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -16987,6 +18512,11 @@
           <t>ZANNI Matteo</t>
         </is>
       </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>98759</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -17051,6 +18581,11 @@
           <t>COF Blaz</t>
         </is>
       </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>36897</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -17115,6 +18650,11 @@
           <t>SUELZER Janosch</t>
         </is>
       </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>43111</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -17179,6 +18719,11 @@
           <t>WEBER Normen</t>
         </is>
       </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>36679</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -17243,6 +18788,11 @@
           <t>ZNIDARCIC Nejc</t>
         </is>
       </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>37764</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -17307,6 +18857,11 @@
           <t>SATKE Adam</t>
         </is>
       </c>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>70681</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -17371,6 +18926,11 @@
           <t>URANKAR Anze</t>
         </is>
       </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>44341</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -17435,6 +18995,11 @@
           <t>MATEJICEK Vojtech</t>
         </is>
       </c>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>87966</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -17499,6 +19064,11 @@
           <t>OVEN Simon</t>
         </is>
       </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>38164</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -17563,6 +19133,11 @@
           <t>LEMMEN Yannic</t>
         </is>
       </c>
+      <c r="X289" t="inlineStr">
+        <is>
+          <t>45115</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -17627,6 +19202,11 @@
           <t>BARONE Luca</t>
         </is>
       </c>
+      <c r="X290" t="inlineStr">
+        <is>
+          <t>94780</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -17691,6 +19271,11 @@
           <t>BOLZERN Linus</t>
         </is>
       </c>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>56069</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -17755,6 +19340,11 @@
           <t>CIOTOLI Francesco</t>
         </is>
       </c>
+      <c r="X292" t="inlineStr">
+        <is>
+          <t>70132</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -17819,6 +19409,11 @@
           <t>ABBIATI Giacomo</t>
         </is>
       </c>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>94769</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -17883,6 +19478,11 @@
           <t>BRETSCHER Cornel</t>
         </is>
       </c>
+      <c r="X294" t="inlineStr">
+        <is>
+          <t>76131</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -17947,6 +19547,11 @@
           <t>CORTI Lorenzo</t>
         </is>
       </c>
+      <c r="X295" t="inlineStr">
+        <is>
+          <t>112761</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -18011,6 +19616,11 @@
           <t>NOVAK Matyas</t>
         </is>
       </c>
+      <c r="X296" t="inlineStr">
+        <is>
+          <t>105998</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -18075,6 +19685,11 @@
           <t>BLAIS Elias</t>
         </is>
       </c>
+      <c r="X297" t="inlineStr">
+        <is>
+          <t>98755</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -18139,6 +19754,11 @@
           <t>PIASKOWSKI Joshua</t>
         </is>
       </c>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>130603</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -18203,6 +19823,11 @@
           <t>PANATO Cecilia</t>
         </is>
       </c>
+      <c r="X299" t="inlineStr">
+        <is>
+          <t>75522</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -18267,6 +19892,11 @@
           <t>NEMCOVA Marie</t>
         </is>
       </c>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>78808</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -18331,6 +19961,11 @@
           <t>FONTAINE Laura</t>
         </is>
       </c>
+      <c r="X301" t="inlineStr">
+        <is>
+          <t>98758</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -18395,6 +20030,11 @@
           <t>GAUBERT Elsa</t>
         </is>
       </c>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>76817</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -18459,6 +20099,11 @@
           <t>DZIADKOVA Zuzana</t>
         </is>
       </c>
+      <c r="X303" t="inlineStr">
+        <is>
+          <t>98317</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -18523,6 +20168,11 @@
           <t>KOPUNOVA Katarina</t>
         </is>
       </c>
+      <c r="X304" t="inlineStr">
+        <is>
+          <t>35471</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -18587,6 +20237,11 @@
           <t>BEZIAT Margot</t>
         </is>
       </c>
+      <c r="X305" t="inlineStr">
+        <is>
+          <t>86154</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -18651,6 +20306,11 @@
           <t>SCHOLCZOVA Viktoria</t>
         </is>
       </c>
+      <c r="X306" t="inlineStr">
+        <is>
+          <t>89134</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -18715,6 +20375,11 @@
           <t>RETKOVA Anna</t>
         </is>
       </c>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>105733</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -18779,6 +20444,11 @@
           <t>GAWEHN Franziska</t>
         </is>
       </c>
+      <c r="X308" t="inlineStr">
+        <is>
+          <t>130600</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -18843,6 +20513,11 @@
           <t>PANATO Alice</t>
         </is>
       </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>56059</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -18907,6 +20582,11 @@
           <t>PLACHTOVA Alexandra</t>
         </is>
       </c>
+      <c r="X310" t="inlineStr">
+        <is>
+          <t>75570</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -18976,6 +20656,16 @@
           <t>ROLENC Ondrej</t>
         </is>
       </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>42246</t>
+        </is>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>35512</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -19045,6 +20735,16 @@
           <t>TROUBADY Pierre</t>
         </is>
       </c>
+      <c r="X312" t="inlineStr">
+        <is>
+          <t>56142</t>
+        </is>
+      </c>
+      <c r="Y312" t="inlineStr">
+        <is>
+          <t>39643</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -19114,6 +20814,16 @@
           <t>ROUSSIN Tanguy</t>
         </is>
       </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>89475</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>89476</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -19183,6 +20893,16 @@
           <t>BIANCHETTI Giacomo</t>
         </is>
       </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>75795</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>75796</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -19252,6 +20972,16 @@
           <t>SCHWARZ Ole</t>
         </is>
       </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>112668</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>76065</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -19315,6 +21045,16 @@
           <t>CARDOSELLI Tomas</t>
         </is>
       </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>112202</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>131360</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -19378,6 +21118,16 @@
           <t>RASNER Karel</t>
         </is>
       </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>98305</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>98298</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -19447,6 +21197,16 @@
           <t>VIENS Theo</t>
         </is>
       </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>63173</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>56129</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -19516,6 +21276,16 @@
           <t>SUELZER Janosch</t>
         </is>
       </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>53557</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>43111</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -19585,6 +21355,16 @@
           <t>WEBER Normen</t>
         </is>
       </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>37668</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>36679</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -19654,6 +21434,16 @@
           <t>BEZIAT Margot</t>
         </is>
       </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>76817</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>86154</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -19723,6 +21513,16 @@
           <t>CLAVADETSCHER Mona</t>
         </is>
       </c>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>63133</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>112429</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -19792,6 +21592,16 @@
           <t>RETKOVA Anna</t>
         </is>
       </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>75570</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>105733</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -19861,6 +21671,16 @@
           <t>STRILKOVA Jana</t>
         </is>
       </c>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>123430</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>104447</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -19930,6 +21750,16 @@
           <t>CHRISTIE Emma</t>
         </is>
       </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>99724</t>
+        </is>
+      </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>99726</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -19999,6 +21829,16 @@
           <t>ROMERO GOMEZ Nuria</t>
         </is>
       </c>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>123935</t>
+        </is>
+      </c>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>131273</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -20068,6 +21908,16 @@
           <t>FEINE Constanze</t>
         </is>
       </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>35175</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>93970</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -20137,6 +21987,16 @@
           <t>KROENER Valentina</t>
         </is>
       </c>
+      <c r="X328" t="inlineStr">
+        <is>
+          <t>41613</t>
+        </is>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>41612</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -20206,6 +22066,16 @@
           <t>DILAI Magdalen</t>
         </is>
       </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>75768</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>75657</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -20275,6 +22145,16 @@
           <t>PANATO Cecilia</t>
         </is>
       </c>
+      <c r="X330" t="inlineStr">
+        <is>
+          <t>56059</t>
+        </is>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>75522</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -20349,6 +22229,21 @@
           <t>URANKAR Anze</t>
         </is>
       </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>37764</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>38164</t>
+        </is>
+      </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>44341</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -20423,6 +22318,21 @@
           <t>PIASKOWSKI Joshua</t>
         </is>
       </c>
+      <c r="X332" t="inlineStr">
+        <is>
+          <t>45115</t>
+        </is>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>37662</t>
+        </is>
+      </c>
+      <c r="Z332" t="inlineStr">
+        <is>
+          <t>130603</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -20497,6 +22407,21 @@
           <t>CORTI Lorenzo</t>
         </is>
       </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>70132</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>94769</t>
+        </is>
+      </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>112761</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -20571,6 +22496,21 @@
           <t>CLAVADETSCHER Luis</t>
         </is>
       </c>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>56069</t>
+        </is>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>76131</t>
+        </is>
+      </c>
+      <c r="Z334" t="inlineStr">
+        <is>
+          <t>97549</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -20645,6 +22585,21 @@
           <t>SATKE Adam</t>
         </is>
       </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>87966</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>105998</t>
+        </is>
+      </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>70681</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -20719,6 +22674,21 @@
           <t>KLEUT Neven</t>
         </is>
       </c>
+      <c r="X336" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>87291</t>
+        </is>
+      </c>
+      <c r="Z336" t="inlineStr">
+        <is>
+          <t>112758</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -20793,6 +22763,21 @@
           <t>GUGINOV Blagoj</t>
         </is>
       </c>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>35591</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>43799</t>
+        </is>
+      </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t>130269</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -20867,6 +22852,21 @@
           <t>RODRIGUEZ LOPEZ Gabriel</t>
         </is>
       </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>37655</t>
+        </is>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>37664</t>
+        </is>
+      </c>
+      <c r="Z338" t="inlineStr">
+        <is>
+          <t>123929</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -20928,7 +22928,7 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>HOLMES Jakob</t>
+          <t>HOLMES Jacob</t>
         </is>
       </c>
       <c r="S339" t="inlineStr">
@@ -20939,6 +22939,16 @@
       <c r="T339" t="inlineStr">
         <is>
           <t>SHEPPY Alexander</t>
+        </is>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>53139</t>
+        </is>
+      </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>77242</t>
         </is>
       </c>
     </row>
@@ -21001,12 +23011,27 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>Bartos Simon</t>
+          <t>BARTOS Simon</t>
         </is>
       </c>
       <c r="T340" t="inlineStr">
         <is>
-          <t>Danik Ladislav</t>
+          <t>DANIK Ladislav</t>
+        </is>
+      </c>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>86453</t>
+        </is>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>113254</t>
+        </is>
+      </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t>82996</t>
         </is>
       </c>
     </row>
@@ -21077,6 +23102,21 @@
           <t>DUVIVIER Alban</t>
         </is>
       </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>70119</t>
+        </is>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>130604</t>
+        </is>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>87608</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -21151,6 +23191,21 @@
           <t>BLAIS Elias</t>
         </is>
       </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>56142</t>
+        </is>
+      </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>94780</t>
+        </is>
+      </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>98755</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -21225,6 +23280,21 @@
           <t>LEBOUC Lisa</t>
         </is>
       </c>
+      <c r="X343" t="inlineStr">
+        <is>
+          <t>53291</t>
+        </is>
+      </c>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>94782</t>
+        </is>
+      </c>
+      <c r="Z343" t="inlineStr">
+        <is>
+          <t>56150</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -21299,6 +23369,21 @@
           <t>MASSINI Christina</t>
         </is>
       </c>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>39763</t>
+        </is>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>36676</t>
+        </is>
+      </c>
+      <c r="Z344" t="inlineStr">
+        <is>
+          <t>87895</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -21373,6 +23458,21 @@
           <t>NOVOSADOVA Kristina</t>
         </is>
       </c>
+      <c r="X345" t="inlineStr">
+        <is>
+          <t>78808</t>
+        </is>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>89349</t>
+        </is>
+      </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>98301</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -21447,6 +23547,21 @@
           <t>MUELLER Hannah</t>
         </is>
       </c>
+      <c r="X346" t="inlineStr">
+        <is>
+          <t>112429</t>
+        </is>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>112430</t>
+        </is>
+      </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t>63133</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -21521,6 +23636,21 @@
           <t>JANCAR Ziva</t>
         </is>
       </c>
+      <c r="X347" t="inlineStr">
+        <is>
+          <t>94495</t>
+        </is>
+      </c>
+      <c r="Y347" t="inlineStr">
+        <is>
+          <t>112182</t>
+        </is>
+      </c>
+      <c r="Z347" t="inlineStr">
+        <is>
+          <t>83919</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -21595,6 +23725,21 @@
           <t>MURRAY Victoria</t>
         </is>
       </c>
+      <c r="X348" t="inlineStr">
+        <is>
+          <t>112780</t>
+        </is>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>75768</t>
+        </is>
+      </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>75660</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -21669,6 +23814,21 @@
           <t>ROMERO GOMEZ Nuria</t>
         </is>
       </c>
+      <c r="X349" t="inlineStr">
+        <is>
+          <t>123935</t>
+        </is>
+      </c>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>112772</t>
+        </is>
+      </c>
+      <c r="Z349" t="inlineStr">
+        <is>
+          <t>131273</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -21743,6 +23903,21 @@
           <t>ZANNI Matteo</t>
         </is>
       </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>63173</t>
+        </is>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>94783</t>
+        </is>
+      </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>98759</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -21817,6 +23992,21 @@
           <t>SALAJ Frantisek</t>
         </is>
       </c>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>35512</t>
+        </is>
+      </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>98305</t>
+        </is>
+      </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>96105</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -21891,6 +24081,21 @@
           <t>HEILINGER Andreas</t>
         </is>
       </c>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>36679</t>
+        </is>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>43111</t>
+        </is>
+      </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>43056</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -21965,6 +24170,21 @@
           <t>MAPELLI Tommaso</t>
         </is>
       </c>
+      <c r="X353" t="inlineStr">
+        <is>
+          <t>110468</t>
+        </is>
+      </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>75796</t>
+        </is>
+      </c>
+      <c r="Z353" t="inlineStr">
+        <is>
+          <t>75795</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -22039,6 +24259,21 @@
           <t>RAMOS COLLADO Rodrigo</t>
         </is>
       </c>
+      <c r="X354" t="inlineStr">
+        <is>
+          <t>71117</t>
+        </is>
+      </c>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>79679</t>
+        </is>
+      </c>
+      <c r="Z354" t="inlineStr">
+        <is>
+          <t>37657</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -22105,12 +24340,27 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>CLAVADETSCHER; Luis</t>
+          <t>CLAVADETSCHER Luis</t>
         </is>
       </c>
       <c r="T355" t="inlineStr">
         <is>
           <t>AMSTAD Janis</t>
+        </is>
+      </c>
+      <c r="X355" t="inlineStr">
+        <is>
+          <t>76129</t>
+        </is>
+      </c>
+      <c r="Y355" t="inlineStr">
+        <is>
+          <t>97549</t>
+        </is>
+      </c>
+      <c r="Z355" t="inlineStr">
+        <is>
+          <t>97548</t>
         </is>
       </c>
     </row>
@@ -22181,6 +24431,21 @@
           <t>SHEPPY Alexander</t>
         </is>
       </c>
+      <c r="X356" t="inlineStr">
+        <is>
+          <t>53139</t>
+        </is>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>121055</t>
+        </is>
+      </c>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t>77242</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -22255,6 +24520,21 @@
           <t>RETKOVA Anna</t>
         </is>
       </c>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>78808</t>
+        </is>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>98317</t>
+        </is>
+      </c>
+      <c r="Z357" t="inlineStr">
+        <is>
+          <t>105733</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -22329,6 +24609,21 @@
           <t>GAUBERT Elsa</t>
         </is>
       </c>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>98758</t>
+        </is>
+      </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>86154</t>
+        </is>
+      </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>76817</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -22397,6 +24692,21 @@
           <t>FEINE Constanze</t>
         </is>
       </c>
+      <c r="X359" t="inlineStr">
+        <is>
+          <t>35175</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>130600</t>
+        </is>
+      </c>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t>93970</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -22465,6 +24775,21 @@
           <t>MURRAY Victoria</t>
         </is>
       </c>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>99724</t>
+        </is>
+      </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>75768</t>
+        </is>
+      </c>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t>75660</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -22554,6 +24879,36 @@
           <t>TROUBADY Pierre</t>
         </is>
       </c>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>63173</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>56129</t>
+        </is>
+      </c>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t>89475</t>
+        </is>
+      </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>89476</t>
+        </is>
+      </c>
+      <c r="AB361" t="inlineStr">
+        <is>
+          <t>56142</t>
+        </is>
+      </c>
+      <c r="AC361" t="inlineStr">
+        <is>
+          <t>39643</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -22643,6 +24998,36 @@
           <t>CARDOSELLI Tomas</t>
         </is>
       </c>
+      <c r="X362" t="inlineStr">
+        <is>
+          <t>42246</t>
+        </is>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>35512</t>
+        </is>
+      </c>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t>98305</t>
+        </is>
+      </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>98298</t>
+        </is>
+      </c>
+      <c r="AB362" t="inlineStr">
+        <is>
+          <t>112202</t>
+        </is>
+      </c>
+      <c r="AC362" t="inlineStr">
+        <is>
+          <t>131360</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -22732,6 +25117,36 @@
           <t>VICENTE VELASCO Ruben</t>
         </is>
       </c>
+      <c r="X363" t="inlineStr">
+        <is>
+          <t>71117</t>
+        </is>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>79679</t>
+        </is>
+      </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>37654</t>
+        </is>
+      </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>112774</t>
+        </is>
+      </c>
+      <c r="AB363" t="inlineStr">
+        <is>
+          <t>37657</t>
+        </is>
+      </c>
+      <c r="AC363" t="inlineStr">
+        <is>
+          <t>131274</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -22819,6 +25234,36 @@
       <c r="W364" t="inlineStr">
         <is>
           <t>SCHWARZ Ole</t>
+        </is>
+      </c>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>37668</t>
+        </is>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>36679</t>
+        </is>
+      </c>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t>53557</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>43111</t>
+        </is>
+      </c>
+      <c r="AB364" t="inlineStr">
+        <is>
+          <t>112668</t>
+        </is>
+      </c>
+      <c r="AC364" t="inlineStr">
+        <is>
+          <t>76065</t>
         </is>
       </c>
     </row>
